--- a/templates_formats/constancia de prestacion de servicios.xlsx
+++ b/templates_formats/constancia de prestacion de servicios.xlsx
@@ -16,10 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
-  <si>
-    <t xml:space="preserve">     Quien suscribe Prof(a),</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>CI dire</t>
   </si>
@@ -36,52 +33,61 @@
     <t>, portador de la cedula de</t>
   </si>
   <si>
-    <t>Constancia que se expide a la peticion de la parte Interesada</t>
+    <t xml:space="preserve">, portador </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> de la CI:</t>
+  </si>
+  <si>
+    <t>se desempeña como:</t>
+  </si>
+  <si>
+    <t>CONSTANCIA DE PRESTACION DE SERVICIOS</t>
+  </si>
+  <si>
+    <t>INSTITUTO NACIONAL "NOMBRE INSTITUTO"</t>
+  </si>
+  <si>
+    <t>CODE DEA "NUMERO CODIGO"</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> "NOMBRE PAIS "</t>
+  </si>
+  <si>
+    <t>MINISTERIO "NOMBRE MINISTERIO"</t>
+  </si>
+  <si>
+    <t>"NOMBRE MUNICIPIO","NOMBRE ESTADO"</t>
+  </si>
+  <si>
+    <t>Nombre Parroquia,</t>
+  </si>
+  <si>
+    <t>,Codigo:</t>
   </si>
   <si>
     <t>el(la) ciudadano(a) :</t>
   </si>
   <si>
-    <t xml:space="preserve">, portador </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> de la CI:</t>
-  </si>
-  <si>
-    <t>se desempeña como:</t>
-  </si>
-  <si>
-    <t>,  Codigo:</t>
-  </si>
-  <si>
     <t>code</t>
   </si>
   <si>
+    <t>hace constar que</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ,Directora(a) de la Institucion "Intituto Nacional Nombre Intituto"</t>
+  </si>
+  <si>
+    <t>interesada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Constancia   que   se   expide   a   la  peticion   de   la  parte </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Quien suscribe Prof(a),</t>
+  </si>
+  <si>
     <t>desde el:</t>
-  </si>
-  <si>
-    <t>CONSTANCIA DE PRESTACION DE SERVICIOS</t>
-  </si>
-  <si>
-    <t>INSTITUTO NACIONAL "NOMBRE INSTITUTO"</t>
-  </si>
-  <si>
-    <t>CODE DEA "NUMERO CODIGO"</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ,Directora(a) de la Institucion "Nombre Instituto" , hace constar que</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> "NOMBRE PAIS "</t>
-  </si>
-  <si>
-    <t>MINISTERIO "NOMBRE MINISTERIO"</t>
-  </si>
-  <si>
-    <t>"NOMBRE MUNICIPIO","NOMBRE ESTADO"</t>
-  </si>
-  <si>
-    <t>Nombre Parroquia,</t>
   </si>
 </sst>
 </file>
@@ -140,7 +146,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -187,29 +193,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="11"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="21"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="15"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="27"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="31"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="33"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="34"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="38"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -512,734 +506,793 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:V70"/>
+  <dimension ref="A1:X70"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="0.875" customWidth="1"/>
-    <col min="2" max="2" width="1" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="5.25" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="8.5" customWidth="1"/>
-    <col min="7" max="7" width="7.25" customWidth="1"/>
-    <col min="8" max="8" width="9.375" customWidth="1"/>
-    <col min="9" max="9" width="7.625" customWidth="1"/>
-    <col min="10" max="10" width="10.75" customWidth="1"/>
-    <col min="11" max="11" width="9.75" customWidth="1"/>
-    <col min="12" max="12" width="11.75" customWidth="1"/>
-    <col min="13" max="13" width="2.875" customWidth="1"/>
-    <col min="14" max="14" width="11.875" customWidth="1"/>
-    <col min="15" max="15" width="12.125" customWidth="1"/>
-    <col min="16" max="16" width="12.625" customWidth="1"/>
-    <col min="17" max="17" width="3.875" customWidth="1"/>
-    <col min="18" max="18" width="9.625" customWidth="1"/>
-    <col min="19" max="19" width="10.25" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
-    <col min="23" max="23" width="9" customWidth="1"/>
+    <col min="1" max="1" width="3" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="0.25" customWidth="1"/>
+    <col min="3" max="3" width="8.875" customWidth="1"/>
+    <col min="4" max="4" width="6.375" customWidth="1"/>
+    <col min="5" max="5" width="2.875" customWidth="1"/>
+    <col min="6" max="6" width="6" customWidth="1"/>
+    <col min="7" max="7" width="2.125" customWidth="1"/>
+    <col min="8" max="8" width="15.375" customWidth="1"/>
+    <col min="9" max="9" width="9" customWidth="1"/>
+    <col min="10" max="10" width="7" customWidth="1"/>
+    <col min="11" max="11" width="8.5" customWidth="1"/>
+    <col min="12" max="12" width="7.5" customWidth="1"/>
+    <col min="13" max="14" width="11.75" customWidth="1"/>
+    <col min="15" max="15" width="2.875" customWidth="1"/>
+    <col min="16" max="16" width="11.875" customWidth="1"/>
+    <col min="17" max="17" width="12.125" customWidth="1"/>
+    <col min="18" max="18" width="12.625" customWidth="1"/>
+    <col min="19" max="19" width="3.875" customWidth="1"/>
+    <col min="20" max="20" width="9.625" customWidth="1"/>
+    <col min="21" max="21" width="10.25" customWidth="1"/>
+    <col min="22" max="22" width="9" customWidth="1"/>
+    <col min="25" max="25" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="C1" s="25" t="s">
-        <v>18</v>
-      </c>
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A1" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
       <c r="D1" s="20"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-    </row>
-    <row r="2" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="C2" s="23" t="s">
-        <v>19</v>
-      </c>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="11"/>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A2" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
       <c r="D2" s="20"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="S2" s="1"/>
-    </row>
-    <row r="3" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="C3" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="20"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
-      <c r="L3" s="12"/>
-    </row>
-    <row r="4" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="C4" s="21" t="s">
-        <v>20</v>
-      </c>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="9"/>
+      <c r="U2" s="1"/>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A3" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="19"/>
+      <c r="L3" s="19"/>
+      <c r="M3" s="19"/>
+      <c r="N3" s="12"/>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A4" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
       <c r="D4" s="20"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
-      <c r="O4" s="5"/>
-    </row>
-    <row r="5" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="C5" s="24" t="s">
-        <v>16</v>
-      </c>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="20"/>
+      <c r="M4" s="20"/>
+      <c r="N4" s="10"/>
+      <c r="Q4" s="5"/>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A5" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
       <c r="D5" s="20"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
-      <c r="L5" s="13"/>
-      <c r="O5" s="2"/>
-      <c r="Q5" s="1"/>
-    </row>
-    <row r="6" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="I6" s="16"/>
-      <c r="N6" s="4"/>
-      <c r="O6" s="2"/>
-      <c r="Q6" s="1"/>
-      <c r="T6" s="3"/>
-    </row>
-    <row r="7" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="G7" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="H7" s="17"/>
-      <c r="M7" s="1"/>
-      <c r="O7" s="2"/>
-      <c r="Q7" s="1"/>
-      <c r="R7" s="1"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="20"/>
+      <c r="M5" s="20"/>
+      <c r="N5" s="13"/>
+      <c r="Q5" s="2"/>
+      <c r="S5" s="1"/>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="K6" s="16"/>
+      <c r="P6" s="4"/>
+      <c r="Q6" s="2"/>
+      <c r="S6" s="1"/>
+      <c r="V6" s="3"/>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="I7" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J7" s="17"/>
+      <c r="O7" s="1"/>
+      <c r="Q7" s="2"/>
       <c r="S7" s="1"/>
       <c r="T7" s="1"/>
       <c r="U7" s="1"/>
-    </row>
-    <row r="8" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="M8" s="1"/>
-      <c r="Q8" s="1"/>
-      <c r="R8" s="1"/>
+      <c r="V7" s="1"/>
+      <c r="W7" s="1"/>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="O8" s="1"/>
       <c r="S8" s="1"/>
       <c r="T8" s="1"/>
       <c r="U8" s="1"/>
-    </row>
-    <row r="9" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="E9" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" s="18"/>
-      <c r="N9" s="1"/>
-      <c r="O9" s="1"/>
+      <c r="V8" s="1"/>
+      <c r="W8" s="1"/>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="C9" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="21"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="21"/>
+      <c r="L9" s="21"/>
+      <c r="M9" s="21"/>
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
       <c r="T9" s="1"/>
       <c r="U9" s="1"/>
-    </row>
-    <row r="10" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="N10" s="1"/>
-      <c r="O10" s="6"/>
-      <c r="P10" s="6"/>
-      <c r="Q10" s="1"/>
-      <c r="R10" s="1"/>
+      <c r="V9" s="1"/>
+      <c r="W9" s="1"/>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="P10" s="1"/>
+      <c r="Q10" s="6"/>
+      <c r="R10" s="6"/>
       <c r="S10" s="1"/>
       <c r="T10" s="1"/>
       <c r="U10" s="1"/>
-    </row>
-    <row r="11" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="V10" s="1"/>
+      <c r="W10" s="1"/>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>0</v>
-      </c>
-      <c r="I11" t="s">
-        <v>5</v>
-      </c>
-      <c r="P11" s="6"/>
-      <c r="Q11" s="1"/>
-      <c r="R11" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="J11" t="s">
+        <v>4</v>
+      </c>
+      <c r="R11" s="6"/>
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
       <c r="U11" s="1"/>
-    </row>
-    <row r="12" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="V11" s="1"/>
+      <c r="W11" s="1"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>4</v>
-      </c>
-      <c r="D12" t="s">
-        <v>17</v>
-      </c>
-      <c r="M12" s="1"/>
-      <c r="P12" s="6"/>
-      <c r="Q12" s="1"/>
-      <c r="R12" s="1"/>
+        <v>3</v>
+      </c>
+      <c r="F12" t="s">
+        <v>19</v>
+      </c>
+      <c r="O12" s="1"/>
+      <c r="R12" s="6"/>
       <c r="S12" s="1"/>
       <c r="T12" s="1"/>
       <c r="U12" s="1"/>
-    </row>
-    <row r="13" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="V12" s="1"/>
+      <c r="W12" s="1"/>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>7</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="I13" t="s">
-        <v>9</v>
-      </c>
-      <c r="P13" s="6"/>
-      <c r="Q13" s="1"/>
-      <c r="R13" s="1"/>
+        <v>18</v>
+      </c>
+      <c r="E13" t="s">
+        <v>16</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="M13" s="5"/>
+      <c r="R13" s="6"/>
       <c r="S13" s="1"/>
       <c r="T13" s="1"/>
       <c r="U13" s="1"/>
-    </row>
-    <row r="14" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="V13" s="1"/>
+      <c r="W13" s="1"/>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>10</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I14" t="s">
-        <v>12</v>
-      </c>
-      <c r="J14" t="s">
-        <v>13</v>
-      </c>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-      <c r="P14" s="6"/>
-      <c r="Q14" s="1"/>
-      <c r="R14" s="1"/>
+        <v>6</v>
+      </c>
+      <c r="F14" t="s">
+        <v>7</v>
+      </c>
+      <c r="L14" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="M14" s="18"/>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1"/>
+      <c r="R14" s="6"/>
       <c r="S14" s="1"/>
       <c r="T14" s="1"/>
       <c r="U14" s="1"/>
-    </row>
-    <row r="15" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="V14" s="1"/>
+      <c r="W14" s="1"/>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
-        <v>6</v>
-      </c>
-      <c r="I15" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="M15" s="1"/>
-      <c r="P15" s="6"/>
-      <c r="Q15" s="1"/>
-      <c r="R15" s="1"/>
+        <v>17</v>
+      </c>
+      <c r="D15" t="s">
+        <v>23</v>
+      </c>
+      <c r="H15" t="s">
+        <v>21</v>
+      </c>
+      <c r="O15" s="1"/>
+      <c r="R15" s="6"/>
       <c r="S15" s="1"/>
       <c r="T15" s="1"/>
       <c r="U15" s="1"/>
-    </row>
-    <row r="16" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-      <c r="P16" s="6"/>
-      <c r="Q16" s="1"/>
-      <c r="R16" s="1"/>
+      <c r="V15" s="1"/>
+      <c r="W15" s="1"/>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="C16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1"/>
+      <c r="R16" s="6"/>
       <c r="S16" s="1"/>
       <c r="T16" s="1"/>
       <c r="U16" s="1"/>
-    </row>
-    <row r="17" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="D17" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="19"/>
-      <c r="M17" s="1"/>
-      <c r="N17" s="1"/>
-      <c r="P17" s="6"/>
-      <c r="Q17" s="1"/>
-      <c r="R17" s="1"/>
+      <c r="V16" s="1"/>
+      <c r="W16" s="1"/>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A17" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="20"/>
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+      <c r="M17" s="20"/>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1"/>
+      <c r="R17" s="6"/>
       <c r="S17" s="1"/>
       <c r="T17" s="1"/>
       <c r="U17" s="1"/>
-    </row>
-    <row r="18" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="D18" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="19"/>
-      <c r="M18" s="1"/>
-      <c r="N18" s="1"/>
-      <c r="P18" s="6"/>
-      <c r="Q18" s="1"/>
-      <c r="R18" s="1"/>
+      <c r="V17" s="1"/>
+      <c r="W17" s="1"/>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A18" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="20"/>
+      <c r="I18" s="20"/>
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+      <c r="M18" s="20"/>
+      <c r="O18" s="1"/>
+      <c r="P18" s="1"/>
+      <c r="R18" s="6"/>
       <c r="S18" s="1"/>
       <c r="T18" s="1"/>
       <c r="U18" s="1"/>
-    </row>
-    <row r="19" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="N19" s="1"/>
-      <c r="P19" s="6"/>
-      <c r="Q19" s="1"/>
-      <c r="R19" s="1"/>
+      <c r="V18" s="1"/>
+      <c r="W18" s="1"/>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="P19" s="1"/>
+      <c r="R19" s="6"/>
       <c r="S19" s="1"/>
       <c r="T19" s="1"/>
       <c r="U19" s="1"/>
-    </row>
-    <row r="20" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="N20" s="1"/>
-      <c r="P20" s="6"/>
-      <c r="Q20" s="1"/>
-      <c r="R20" s="1"/>
+      <c r="V19" s="1"/>
+      <c r="W19" s="1"/>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="P20" s="1"/>
+      <c r="R20" s="6"/>
       <c r="S20" s="1"/>
       <c r="T20" s="1"/>
       <c r="U20" s="1"/>
-    </row>
-    <row r="21" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="P21" s="6"/>
-      <c r="Q21" s="1"/>
-      <c r="R21" s="1"/>
+      <c r="V20" s="1"/>
+      <c r="W20" s="1"/>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="R21" s="6"/>
       <c r="S21" s="1"/>
       <c r="T21" s="1"/>
       <c r="U21" s="1"/>
-    </row>
-    <row r="22" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="P22" s="7"/>
-      <c r="Q22" s="1"/>
-      <c r="R22" s="1"/>
+      <c r="V21" s="1"/>
+      <c r="W21" s="1"/>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="R22" s="7"/>
       <c r="S22" s="1"/>
       <c r="T22" s="1"/>
       <c r="U22" s="1"/>
-    </row>
-    <row r="23" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="M23" s="1"/>
+      <c r="V22" s="1"/>
+      <c r="W22" s="1"/>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
       <c r="O23" s="1"/>
-      <c r="P23" s="6"/>
       <c r="Q23" s="1"/>
-      <c r="R23" s="1"/>
+      <c r="R23" s="6"/>
       <c r="S23" s="1"/>
       <c r="T23" s="1"/>
       <c r="U23" s="1"/>
-    </row>
-    <row r="24" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="M24" s="15"/>
-      <c r="N24" s="1"/>
-      <c r="O24" s="6"/>
-      <c r="P24" s="6"/>
-      <c r="Q24" s="1"/>
-      <c r="R24" s="1"/>
+      <c r="V23" s="1"/>
+      <c r="W23" s="1"/>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="O24" s="15"/>
+      <c r="P24" s="1"/>
+      <c r="Q24" s="6"/>
+      <c r="R24" s="6"/>
       <c r="S24" s="1"/>
       <c r="T24" s="1"/>
       <c r="U24" s="1"/>
-    </row>
-    <row r="25" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="M25" s="1"/>
-      <c r="N25" s="1"/>
-      <c r="O25" s="6"/>
-      <c r="P25" s="6"/>
-      <c r="Q25" s="1"/>
-      <c r="R25" s="1"/>
+      <c r="V24" s="1"/>
+      <c r="W24" s="1"/>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="O25" s="1"/>
+      <c r="P25" s="1"/>
+      <c r="Q25" s="6"/>
+      <c r="R25" s="6"/>
       <c r="S25" s="1"/>
       <c r="T25" s="1"/>
       <c r="U25" s="1"/>
-    </row>
-    <row r="26" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="M26" s="1"/>
-      <c r="N26" s="1"/>
-      <c r="O26" s="6"/>
-      <c r="P26" s="6"/>
-      <c r="Q26" s="1"/>
-      <c r="R26" s="1"/>
+      <c r="V25" s="1"/>
+      <c r="W25" s="1"/>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="O26" s="1"/>
+      <c r="P26" s="1"/>
+      <c r="Q26" s="6"/>
+      <c r="R26" s="6"/>
       <c r="S26" s="1"/>
       <c r="T26" s="1"/>
       <c r="U26" s="1"/>
-    </row>
-    <row r="27" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="M27" s="1"/>
-      <c r="N27" s="1"/>
-      <c r="O27" s="6"/>
-      <c r="S27" s="1"/>
-      <c r="T27" s="1"/>
+      <c r="V26" s="1"/>
+      <c r="W26" s="1"/>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="O27" s="1"/>
+      <c r="P27" s="1"/>
+      <c r="Q27" s="6"/>
       <c r="U27" s="1"/>
-    </row>
-    <row r="28" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="M28" s="1"/>
-      <c r="N28" s="1"/>
-      <c r="O28" s="6"/>
-      <c r="S28" s="1"/>
-      <c r="T28" s="1"/>
+      <c r="V27" s="1"/>
+      <c r="W27" s="1"/>
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="O28" s="1"/>
+      <c r="P28" s="1"/>
+      <c r="Q28" s="6"/>
       <c r="U28" s="1"/>
-    </row>
-    <row r="29" spans="2:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V28" s="1"/>
+      <c r="W28" s="1"/>
+    </row>
+    <row r="29" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B29" s="1"/>
-      <c r="N29" s="1"/>
-      <c r="O29" s="6"/>
-      <c r="R29" s="1"/>
-      <c r="S29" s="1"/>
+      <c r="P29" s="1"/>
+      <c r="Q29" s="6"/>
       <c r="T29" s="1"/>
       <c r="U29" s="1"/>
-    </row>
-    <row r="30" spans="2:21" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V29" s="1"/>
+      <c r="W29" s="1"/>
+    </row>
+    <row r="30" spans="1:23" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="14"/>
-      <c r="M30" s="1"/>
-      <c r="O30" s="6"/>
-      <c r="R30" s="1"/>
-      <c r="S30" s="1"/>
+      <c r="O30" s="1"/>
+      <c r="Q30" s="6"/>
       <c r="T30" s="1"/>
       <c r="U30" s="1"/>
-    </row>
-    <row r="31" spans="2:21" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V30" s="1"/>
+      <c r="W30" s="1"/>
+    </row>
+    <row r="31" spans="1:23" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B31" s="14"/>
-      <c r="M31" s="1"/>
-      <c r="Q31" s="1"/>
-      <c r="R31" s="1"/>
+      <c r="O31" s="1"/>
       <c r="S31" s="1"/>
       <c r="T31" s="1"/>
       <c r="U31" s="1"/>
-    </row>
-    <row r="32" spans="2:21" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V31" s="1"/>
+      <c r="W31" s="1"/>
+    </row>
+    <row r="32" spans="1:23" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B32" s="14"/>
-      <c r="M32" s="1"/>
-      <c r="O32" s="8"/>
-      <c r="Q32" s="1"/>
+      <c r="O32" s="1"/>
+      <c r="Q32" s="8"/>
       <c r="S32" s="1"/>
-      <c r="T32" s="1"/>
       <c r="U32" s="1"/>
-    </row>
-    <row r="33" spans="2:21" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V32" s="1"/>
+      <c r="W32" s="1"/>
+    </row>
+    <row r="33" spans="2:23" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" s="14"/>
-      <c r="P33" s="6"/>
-      <c r="Q33" s="1"/>
+      <c r="R33" s="6"/>
       <c r="S33" s="1"/>
-      <c r="T33" s="1"/>
       <c r="U33" s="1"/>
-    </row>
-    <row r="34" spans="2:21" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V33" s="1"/>
+      <c r="W33" s="1"/>
+    </row>
+    <row r="34" spans="2:23" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B34" s="14"/>
-      <c r="O34" s="6"/>
-      <c r="R34" s="1"/>
-      <c r="S34" s="1"/>
+      <c r="Q34" s="6"/>
       <c r="T34" s="1"/>
       <c r="U34" s="1"/>
-    </row>
-    <row r="35" spans="2:21" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V34" s="1"/>
+      <c r="W34" s="1"/>
+    </row>
+    <row r="35" spans="2:23" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B35" s="14"/>
-      <c r="R35" s="1"/>
-      <c r="S35" s="1"/>
       <c r="T35" s="1"/>
       <c r="U35" s="1"/>
-    </row>
-    <row r="36" spans="2:21" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V35" s="1"/>
+      <c r="W35" s="1"/>
+    </row>
+    <row r="36" spans="2:23" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="14"/>
-      <c r="P36" s="6"/>
-      <c r="Q36" s="1"/>
-      <c r="R36" s="1"/>
+      <c r="R36" s="6"/>
       <c r="S36" s="1"/>
       <c r="T36" s="1"/>
       <c r="U36" s="1"/>
-    </row>
-    <row r="37" spans="2:21" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="O37" s="6"/>
-      <c r="P37" s="6"/>
-      <c r="Q37" s="1"/>
-      <c r="R37" s="1"/>
+      <c r="V36" s="1"/>
+      <c r="W36" s="1"/>
+    </row>
+    <row r="37" spans="2:23" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="Q37" s="6"/>
+      <c r="R37" s="6"/>
       <c r="S37" s="1"/>
       <c r="T37" s="1"/>
       <c r="U37" s="1"/>
-    </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="O38" s="6"/>
-      <c r="P38" s="6"/>
-      <c r="Q38" s="1"/>
-      <c r="R38" s="1"/>
+      <c r="V37" s="1"/>
+      <c r="W37" s="1"/>
+    </row>
+    <row r="38" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="Q38" s="6"/>
+      <c r="R38" s="6"/>
       <c r="S38" s="1"/>
       <c r="T38" s="1"/>
       <c r="U38" s="1"/>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="O39" s="6"/>
-      <c r="Q39" s="1"/>
-      <c r="R39" s="1"/>
+      <c r="V38" s="1"/>
+      <c r="W38" s="1"/>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="Q39" s="6"/>
       <c r="S39" s="1"/>
       <c r="T39" s="1"/>
       <c r="U39" s="1"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="Q40" s="1"/>
-      <c r="R40" s="1"/>
+      <c r="V39" s="1"/>
+      <c r="W39" s="1"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.25">
       <c r="S40" s="1"/>
       <c r="T40" s="1"/>
       <c r="U40" s="1"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="P41" s="6"/>
-      <c r="Q41" s="1"/>
-      <c r="R41" s="1"/>
+      <c r="V40" s="1"/>
+      <c r="W40" s="1"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="R41" s="6"/>
       <c r="S41" s="1"/>
       <c r="T41" s="1"/>
       <c r="U41" s="1"/>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="O42" s="6"/>
-      <c r="P42" s="6"/>
-      <c r="Q42" s="1"/>
-      <c r="R42" s="1"/>
+      <c r="V41" s="1"/>
+      <c r="W41" s="1"/>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="Q42" s="6"/>
+      <c r="R42" s="6"/>
       <c r="S42" s="1"/>
       <c r="T42" s="1"/>
       <c r="U42" s="1"/>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="O43" s="6"/>
-      <c r="P43" s="6"/>
-      <c r="Q43" s="1"/>
-      <c r="R43" s="1"/>
+      <c r="V42" s="1"/>
+      <c r="W42" s="1"/>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="Q43" s="6"/>
+      <c r="R43" s="6"/>
       <c r="S43" s="1"/>
       <c r="T43" s="1"/>
       <c r="U43" s="1"/>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="O44" s="6"/>
-      <c r="P44" s="6"/>
-      <c r="Q44" s="1"/>
-      <c r="R44" s="1"/>
+      <c r="V43" s="1"/>
+      <c r="W43" s="1"/>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="Q44" s="6"/>
+      <c r="R44" s="6"/>
       <c r="S44" s="1"/>
       <c r="T44" s="1"/>
       <c r="U44" s="1"/>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="O45" s="6"/>
-      <c r="P45" s="6"/>
-      <c r="Q45" s="1"/>
-      <c r="R45" s="1"/>
+      <c r="V44" s="1"/>
+      <c r="W44" s="1"/>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="Q45" s="6"/>
+      <c r="R45" s="6"/>
       <c r="S45" s="1"/>
       <c r="T45" s="1"/>
       <c r="U45" s="1"/>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="O46" s="6"/>
-      <c r="P46" s="6"/>
-      <c r="Q46" s="1"/>
-      <c r="R46" s="1"/>
+      <c r="V45" s="1"/>
+      <c r="W45" s="1"/>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="Q46" s="6"/>
+      <c r="R46" s="6"/>
       <c r="S46" s="1"/>
       <c r="T46" s="1"/>
       <c r="U46" s="1"/>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="O47" s="6"/>
-      <c r="P47" s="6"/>
-      <c r="Q47" s="1"/>
-      <c r="R47" s="1"/>
+      <c r="V46" s="1"/>
+      <c r="W46" s="1"/>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="Q47" s="6"/>
+      <c r="R47" s="6"/>
       <c r="S47" s="1"/>
       <c r="T47" s="1"/>
       <c r="U47" s="1"/>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="O48" s="6"/>
-      <c r="P48" s="6"/>
-      <c r="Q48" s="1"/>
-      <c r="R48" s="1"/>
+      <c r="V47" s="1"/>
+      <c r="W47" s="1"/>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="Q48" s="6"/>
+      <c r="R48" s="6"/>
       <c r="S48" s="1"/>
       <c r="T48" s="1"/>
       <c r="U48" s="1"/>
-    </row>
-    <row r="49" spans="15:21" x14ac:dyDescent="0.25">
-      <c r="O49" s="6"/>
-      <c r="P49" s="6"/>
-      <c r="Q49" s="1"/>
-      <c r="R49" s="1"/>
+      <c r="V48" s="1"/>
+      <c r="W48" s="1"/>
+    </row>
+    <row r="49" spans="17:23" x14ac:dyDescent="0.25">
+      <c r="Q49" s="6"/>
+      <c r="R49" s="6"/>
       <c r="S49" s="1"/>
       <c r="T49" s="1"/>
       <c r="U49" s="1"/>
-    </row>
-    <row r="50" spans="15:21" x14ac:dyDescent="0.25">
-      <c r="O50" s="6"/>
-      <c r="P50" s="1"/>
-      <c r="Q50" s="1"/>
+      <c r="V49" s="1"/>
+      <c r="W49" s="1"/>
+    </row>
+    <row r="50" spans="17:23" x14ac:dyDescent="0.25">
+      <c r="Q50" s="6"/>
       <c r="R50" s="1"/>
       <c r="S50" s="1"/>
       <c r="T50" s="1"/>
       <c r="U50" s="1"/>
-    </row>
-    <row r="51" spans="15:21" x14ac:dyDescent="0.25">
-      <c r="O51" s="1"/>
-      <c r="P51" s="1"/>
+      <c r="V50" s="1"/>
+      <c r="W50" s="1"/>
+    </row>
+    <row r="51" spans="17:23" x14ac:dyDescent="0.25">
       <c r="Q51" s="1"/>
       <c r="R51" s="1"/>
       <c r="S51" s="1"/>
       <c r="T51" s="1"/>
       <c r="U51" s="1"/>
-    </row>
-    <row r="52" spans="15:21" x14ac:dyDescent="0.25">
-      <c r="O52" s="1"/>
-      <c r="P52" s="1"/>
+      <c r="V51" s="1"/>
+      <c r="W51" s="1"/>
+    </row>
+    <row r="52" spans="17:23" x14ac:dyDescent="0.25">
       <c r="Q52" s="1"/>
       <c r="R52" s="1"/>
       <c r="S52" s="1"/>
       <c r="T52" s="1"/>
       <c r="U52" s="1"/>
-    </row>
-    <row r="53" spans="15:21" x14ac:dyDescent="0.25">
-      <c r="O53" s="1"/>
-      <c r="P53" s="1"/>
+      <c r="V52" s="1"/>
+      <c r="W52" s="1"/>
+    </row>
+    <row r="53" spans="17:23" x14ac:dyDescent="0.25">
       <c r="Q53" s="1"/>
       <c r="R53" s="1"/>
       <c r="S53" s="1"/>
       <c r="T53" s="1"/>
       <c r="U53" s="1"/>
-    </row>
-    <row r="54" spans="15:21" x14ac:dyDescent="0.25">
-      <c r="O54" s="1"/>
-      <c r="P54" s="1"/>
+      <c r="V53" s="1"/>
+      <c r="W53" s="1"/>
+    </row>
+    <row r="54" spans="17:23" x14ac:dyDescent="0.25">
       <c r="Q54" s="1"/>
       <c r="R54" s="1"/>
       <c r="S54" s="1"/>
       <c r="T54" s="1"/>
       <c r="U54" s="1"/>
-    </row>
-    <row r="55" spans="15:21" x14ac:dyDescent="0.25">
-      <c r="O55" s="1"/>
-      <c r="P55" s="1"/>
+      <c r="V54" s="1"/>
+      <c r="W54" s="1"/>
+    </row>
+    <row r="55" spans="17:23" x14ac:dyDescent="0.25">
       <c r="Q55" s="1"/>
       <c r="R55" s="1"/>
       <c r="S55" s="1"/>
       <c r="T55" s="1"/>
       <c r="U55" s="1"/>
-    </row>
-    <row r="56" spans="15:21" x14ac:dyDescent="0.25">
-      <c r="O56" s="1"/>
-      <c r="P56" s="1"/>
+      <c r="V55" s="1"/>
+      <c r="W55" s="1"/>
+    </row>
+    <row r="56" spans="17:23" x14ac:dyDescent="0.25">
       <c r="Q56" s="1"/>
       <c r="R56" s="1"/>
       <c r="S56" s="1"/>
       <c r="T56" s="1"/>
       <c r="U56" s="1"/>
-    </row>
-    <row r="57" spans="15:21" x14ac:dyDescent="0.25">
-      <c r="O57" s="1"/>
-      <c r="P57" s="1"/>
+      <c r="V56" s="1"/>
+      <c r="W56" s="1"/>
+    </row>
+    <row r="57" spans="17:23" x14ac:dyDescent="0.25">
       <c r="Q57" s="1"/>
       <c r="R57" s="1"/>
       <c r="S57" s="1"/>
       <c r="T57" s="1"/>
       <c r="U57" s="1"/>
-    </row>
-    <row r="58" spans="15:21" x14ac:dyDescent="0.25">
-      <c r="O58" s="1"/>
-      <c r="P58" s="1"/>
+      <c r="V57" s="1"/>
+      <c r="W57" s="1"/>
+    </row>
+    <row r="58" spans="17:23" x14ac:dyDescent="0.25">
       <c r="Q58" s="1"/>
       <c r="R58" s="1"/>
       <c r="S58" s="1"/>
       <c r="T58" s="1"/>
       <c r="U58" s="1"/>
-    </row>
-    <row r="59" spans="15:21" x14ac:dyDescent="0.25">
-      <c r="O59" s="1"/>
-      <c r="P59" s="1"/>
+      <c r="V58" s="1"/>
+      <c r="W58" s="1"/>
+    </row>
+    <row r="59" spans="17:23" x14ac:dyDescent="0.25">
       <c r="Q59" s="1"/>
       <c r="R59" s="1"/>
       <c r="S59" s="1"/>
       <c r="T59" s="1"/>
       <c r="U59" s="1"/>
-    </row>
-    <row r="60" spans="15:21" x14ac:dyDescent="0.25">
-      <c r="O60" s="1"/>
-      <c r="P60" s="1"/>
+      <c r="V59" s="1"/>
+      <c r="W59" s="1"/>
+    </row>
+    <row r="60" spans="17:23" x14ac:dyDescent="0.25">
       <c r="Q60" s="1"/>
       <c r="R60" s="1"/>
       <c r="S60" s="1"/>
       <c r="T60" s="1"/>
       <c r="U60" s="1"/>
-    </row>
-    <row r="61" spans="15:21" x14ac:dyDescent="0.25">
-      <c r="O61" s="1"/>
-      <c r="P61" s="1"/>
+      <c r="V60" s="1"/>
+      <c r="W60" s="1"/>
+    </row>
+    <row r="61" spans="17:23" x14ac:dyDescent="0.25">
       <c r="Q61" s="1"/>
       <c r="R61" s="1"/>
       <c r="S61" s="1"/>
       <c r="T61" s="1"/>
       <c r="U61" s="1"/>
-    </row>
-    <row r="62" spans="15:21" x14ac:dyDescent="0.25">
-      <c r="O62" s="1"/>
-      <c r="P62" s="1"/>
+      <c r="V61" s="1"/>
+      <c r="W61" s="1"/>
+    </row>
+    <row r="62" spans="17:23" x14ac:dyDescent="0.25">
       <c r="Q62" s="1"/>
       <c r="R62" s="1"/>
       <c r="S62" s="1"/>
       <c r="T62" s="1"/>
       <c r="U62" s="1"/>
-    </row>
-    <row r="63" spans="15:21" x14ac:dyDescent="0.25">
-      <c r="O63" s="1"/>
-      <c r="P63" s="1"/>
+      <c r="V62" s="1"/>
+      <c r="W62" s="1"/>
+    </row>
+    <row r="63" spans="17:23" x14ac:dyDescent="0.25">
       <c r="Q63" s="1"/>
       <c r="R63" s="1"/>
       <c r="S63" s="1"/>
       <c r="T63" s="1"/>
       <c r="U63" s="1"/>
-    </row>
-    <row r="64" spans="15:21" x14ac:dyDescent="0.25">
-      <c r="O64" s="1"/>
-      <c r="P64" s="1"/>
+      <c r="V63" s="1"/>
+      <c r="W63" s="1"/>
+    </row>
+    <row r="64" spans="17:23" x14ac:dyDescent="0.25">
       <c r="Q64" s="1"/>
       <c r="R64" s="1"/>
       <c r="S64" s="1"/>
       <c r="T64" s="1"/>
       <c r="U64" s="1"/>
-    </row>
-    <row r="65" spans="15:22" x14ac:dyDescent="0.25">
-      <c r="O65" s="1"/>
-      <c r="P65" s="1"/>
+      <c r="V64" s="1"/>
+      <c r="W64" s="1"/>
+    </row>
+    <row r="65" spans="17:24" x14ac:dyDescent="0.25">
       <c r="Q65" s="1"/>
       <c r="R65" s="1"/>
       <c r="S65" s="1"/>
       <c r="T65" s="1"/>
       <c r="U65" s="1"/>
-    </row>
-    <row r="66" spans="15:22" x14ac:dyDescent="0.25">
-      <c r="O66" s="1"/>
-      <c r="P66" s="1"/>
+      <c r="V65" s="1"/>
+      <c r="W65" s="1"/>
+    </row>
+    <row r="66" spans="17:24" x14ac:dyDescent="0.25">
       <c r="Q66" s="1"/>
       <c r="R66" s="1"/>
       <c r="S66" s="1"/>
       <c r="T66" s="1"/>
       <c r="U66" s="1"/>
       <c r="V66" s="1"/>
-    </row>
-    <row r="67" spans="15:22" x14ac:dyDescent="0.25">
-      <c r="O67" s="1"/>
-      <c r="P67" s="1"/>
+      <c r="W66" s="1"/>
+      <c r="X66" s="1"/>
+    </row>
+    <row r="67" spans="17:24" x14ac:dyDescent="0.25">
       <c r="Q67" s="1"/>
-    </row>
-    <row r="68" spans="15:22" x14ac:dyDescent="0.25">
-      <c r="O68" s="1"/>
-      <c r="P68" s="1"/>
-    </row>
-    <row r="69" spans="15:22" x14ac:dyDescent="0.25">
-      <c r="O69" s="1"/>
-      <c r="P69" s="1"/>
-    </row>
-    <row r="70" spans="15:22" x14ac:dyDescent="0.25">
-      <c r="O70" s="1"/>
-      <c r="P70" s="1"/>
+      <c r="R67" s="1"/>
+      <c r="S67" s="1"/>
+    </row>
+    <row r="68" spans="17:24" x14ac:dyDescent="0.25">
+      <c r="Q68" s="1"/>
+      <c r="R68" s="1"/>
+    </row>
+    <row r="69" spans="17:24" x14ac:dyDescent="0.25">
+      <c r="Q69" s="1"/>
+      <c r="R69" s="1"/>
+    </row>
+    <row r="70" spans="17:24" x14ac:dyDescent="0.25">
+      <c r="Q70" s="1"/>
+      <c r="R70" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="D18:H18"/>
+  <mergeCells count="7">
+    <mergeCell ref="A17:M17"/>
+    <mergeCell ref="A18:M18"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A4:M4"/>
+    <mergeCell ref="A5:M5"/>
+    <mergeCell ref="C9:M9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
